--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0003.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0003.xlsx
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Allt ägs av staten</t>
+          <t>Produktionsmedel ägs av staten</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Inga pengar används</t>
+          <t>Priser och löner styrs av staten</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Arbete är förbjudet</t>
+          <t>Varor fördelas utan marknad</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Rätt att bli kung</t>
+          <t>Föreningsfrihet</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Rätt att slippa lagar</t>
+          <t>Åtta timmars arbetsdag</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Rätt att stoppa skolan</t>
+          <t>Rätt till strejk</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Alla jobbade i gruvor</t>
+          <t>De flesta arbetade i jordbruket</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Fabriker var förbjudna</t>
+          <t>Industrialiseringen kom sent</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Alla flyttade utomlands</t>
+          <t>Fabrikerna var få och små</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Pyramider</t>
+          <t>Hamnar och fyrar</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Kanaler till Sahara</t>
+          <t>Kanaler och slussar</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Mur runt landet</t>
+          <t>Broar och postrutter</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Slott i varje by</t>
+          <t>Sågverk och bruk</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Guldgruvor i söder</t>
+          <t>Verkstäder</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Vulkanobservatorier</t>
+          <t>Textilindustri</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Endast militärläger</t>
+          <t>Folkbibliotek</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot undervisning</t>
+          <t>Folkbildningsföreningar</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Bara universitet i utlandet</t>
+          <t>Tidningar och tidskrifter</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Flyga flygplan</t>
+          <t>Räkning</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Bygga robotar</t>
+          <t>Kristendomskunskap</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Tala latin som modersmål</t>
+          <t>Geografi</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Förbjöd val</t>
+          <t>Läste tidningar och följde nyheter</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Slutade läsa</t>
+          <t>Gick på möten och debatter</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Brände böcker</t>
+          <t>Skrev insändare och petitionerade</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Slutade arbeta</t>
+          <t>Ställde upp i lokala val</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Flyttade alla till skogen</t>
+          <t>Demonstrerade och ordnade möten</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Förbjöd möten</t>
+          <t>Skrev opinionstexter och namnlistor</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Alla nationer bör försvinna</t>
+          <t>En stat bör omfatta flera nationer</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Språk är oviktigt</t>
+          <t>Nationstillhörighet avgörs av medborgarskap</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Religion ska vara förbjuden</t>
+          <t>En nation är främst en ekonomisk enhet</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Endast pengar</t>
+          <t>Ekonomi, militärmakt och gränser</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Bara väder</t>
+          <t>Medborgarskap och pass</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Bara matvanor</t>
+          <t>Naturresurser och handel</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Total fred överallt</t>
+          <t>Nya gränsdragningar och konflikter</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Inga gränser alls</t>
+          <t>Större rivalitet mellan stater</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Att val avskaffades i alla länder</t>
+          <t>Fullständig politisk enighet i Europa</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Kungligt råd</t>
+          <t>Senaten</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
+          <t>Statsrådet</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
           <t>Ståndsriksdagen i Sverige</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>EU-kommissionen</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
